--- a/ott.xlsx
+++ b/ott.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SkyTam\Desktop\cham-cong\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SkyTam\Desktop\cham-cong\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC061C3D-0065-4943-9CF8-20DD22E85A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028F1AB5-6D1E-489A-B5D9-F9234658F67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Tăng ca</t>
   </si>
@@ -50,39 +50,6 @@
   </si>
   <si>
     <t>Trạng thái phê duyệt</t>
-  </si>
-  <si>
-    <t>X1 Xi Line 1-1</t>
-  </si>
-  <si>
-    <t>Xin làm thêm</t>
-  </si>
-  <si>
-    <t>Phê duyệt</t>
-  </si>
-  <si>
-    <t>A049</t>
-  </si>
-  <si>
-    <t>Phạm Tấn Việt</t>
-  </si>
-  <si>
-    <t>2021-01-20 18:00:00</t>
-  </si>
-  <si>
-    <t>2021-01-20 22:00:00</t>
-  </si>
-  <si>
-    <t>2022-01-18 00:08:16</t>
-  </si>
-  <si>
-    <t>2021-01-19 18:00:00</t>
-  </si>
-  <si>
-    <t>2021-01-19 23:00:00</t>
-  </si>
-  <si>
-    <t>2022-01-18 00:07:51</t>
   </si>
   <si>
     <t>Công ty TNHH Sản Xuất Hiệp Phước Thành</t>
@@ -525,7 +492,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -579,58 +546,26 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
